--- a/sampleprojects/CorporateTax/excel/states/OK_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/OK_corp.xlsx
@@ -193,13 +193,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
+    <t>ok_apportionment</t>
   </si>
   <si>
     <t>(3 attributes)</t>
   </si>
   <si>
-    <t>ok_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>double</t>
@@ -214,7 +214,7 @@
     <t>OK economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>ok_state_tax_rate</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.040</t>
@@ -223,7 +223,7 @@
     <t>OK corporate income tax rate: 4.0% flat rate (68 Okla. Stat. § 2355)</t>
   </si>
   <si>
-    <t>ok_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
